--- a/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9738_colegio-parque-las-americas_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F3B070-C1A0-419E-9C75-C5E01375345F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD57C712-16DA-45EE-B9E3-F09C97FD8890}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31FD21B8-1CC5-4107-AC95-CFCF62BCC844}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F19EE20F-0CCC-41CD-8165-D080A8604BB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{934CE966-D4E1-4259-A43E-7BABB78888E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39650340-DCF6-41AA-9C86-5E208F513648}"/>
 </file>